--- a/Simulacao_Resultados_ENEM_Regioes_2015_2023.xlsx
+++ b/Simulacao_Resultados_ENEM_Regioes_2015_2023.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/904989930feeffce/Documentos/GitHub/Dados-Simulados/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_5FD845B8BB86E9BA01FD8390E22D62B160B64849" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A911CEA3-AFA9-4804-9BF6-B4430E4C3275}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="1060" yWindow="1060" windowWidth="17140" windowHeight="9910" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -64,8 +70,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -128,13 +134,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -172,7 +186,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -206,6 +220,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -240,9 +255,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -415,11 +431,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E226"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.90625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -436,7 +459,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -447,13 +470,13 @@
         <v>10</v>
       </c>
       <c r="D2">
-        <v>524.8</v>
+        <v>524.79999999999995</v>
       </c>
       <c r="E2">
         <v>279178</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -470,7 +493,7 @@
         <v>139879</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -487,7 +510,7 @@
         <v>495602</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -504,7 +527,7 @@
         <v>450410</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -521,7 +544,7 @@
         <v>211335</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -538,7 +561,7 @@
         <v>298167</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -555,7 +578,7 @@
         <v>341879</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -572,7 +595,7 @@
         <v>214027</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>5</v>
       </c>
@@ -589,7 +612,7 @@
         <v>366622</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>5</v>
       </c>
@@ -606,7 +629,7 @@
         <v>404681</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>5</v>
       </c>
@@ -623,7 +646,7 @@
         <v>448989</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -640,7 +663,7 @@
         <v>401490</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>5</v>
       </c>
@@ -657,7 +680,7 @@
         <v>398360</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>5</v>
       </c>
@@ -674,7 +697,7 @@
         <v>293538</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -691,7 +714,7 @@
         <v>276840</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>5</v>
       </c>
@@ -708,7 +731,7 @@
         <v>493254</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>5</v>
       </c>
@@ -725,7 +748,7 @@
         <v>437113</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>5</v>
       </c>
@@ -742,7 +765,7 @@
         <v>88148</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -759,7 +782,7 @@
         <v>174555</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>5</v>
       </c>
@@ -776,7 +799,7 @@
         <v>406502</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>5</v>
       </c>
@@ -793,7 +816,7 @@
         <v>126530</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>5</v>
       </c>
@@ -804,13 +827,13 @@
         <v>11</v>
       </c>
       <c r="D23">
-        <v>518.7</v>
+        <v>518.70000000000005</v>
       </c>
       <c r="E23">
         <v>100077</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>5</v>
       </c>
@@ -827,7 +850,7 @@
         <v>301601</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>5</v>
       </c>
@@ -844,7 +867,7 @@
         <v>479773</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>5</v>
       </c>
@@ -861,7 +884,7 @@
         <v>191829</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>5</v>
       </c>
@@ -872,13 +895,13 @@
         <v>10</v>
       </c>
       <c r="D27">
-        <v>559.7</v>
+        <v>559.70000000000005</v>
       </c>
       <c r="E27">
         <v>291836</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>5</v>
       </c>
@@ -895,7 +918,7 @@
         <v>60397</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>5</v>
       </c>
@@ -912,7 +935,7 @@
         <v>277750</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>5</v>
       </c>
@@ -923,13 +946,13 @@
         <v>13</v>
       </c>
       <c r="D30">
-        <v>528.2</v>
+        <v>528.20000000000005</v>
       </c>
       <c r="E30">
         <v>240884</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>5</v>
       </c>
@@ -946,7 +969,7 @@
         <v>43247</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -957,13 +980,13 @@
         <v>10</v>
       </c>
       <c r="D32">
-        <v>513.2</v>
+        <v>513.20000000000005</v>
       </c>
       <c r="E32">
         <v>368951</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>5</v>
       </c>
@@ -980,7 +1003,7 @@
         <v>294329</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>5</v>
       </c>
@@ -997,7 +1020,7 @@
         <v>256584</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>5</v>
       </c>
@@ -1014,7 +1037,7 @@
         <v>58044</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>5</v>
       </c>
@@ -1031,7 +1054,7 @@
         <v>33986</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>5</v>
       </c>
@@ -1048,7 +1071,7 @@
         <v>81858</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>5</v>
       </c>
@@ -1065,7 +1088,7 @@
         <v>304806</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>5</v>
       </c>
@@ -1082,7 +1105,7 @@
         <v>290536</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1099,7 +1122,7 @@
         <v>371279</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>5</v>
       </c>
@@ -1116,7 +1139,7 @@
         <v>409622</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>5</v>
       </c>
@@ -1133,7 +1156,7 @@
         <v>497867</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>5</v>
       </c>
@@ -1150,7 +1173,7 @@
         <v>476551</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>5</v>
       </c>
@@ -1167,7 +1190,7 @@
         <v>395396</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>5</v>
       </c>
@@ -1184,7 +1207,7 @@
         <v>159182</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>5</v>
       </c>
@@ -1201,7 +1224,7 @@
         <v>118806</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>6</v>
       </c>
@@ -1212,13 +1235,13 @@
         <v>10</v>
       </c>
       <c r="D47">
-        <v>539.8</v>
+        <v>539.79999999999995</v>
       </c>
       <c r="E47">
         <v>420126</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>6</v>
       </c>
@@ -1235,7 +1258,7 @@
         <v>43419</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>6</v>
       </c>
@@ -1252,7 +1275,7 @@
         <v>463852</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>6</v>
       </c>
@@ -1269,7 +1292,7 @@
         <v>142096</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>6</v>
       </c>
@@ -1286,7 +1309,7 @@
         <v>127059</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>6</v>
       </c>
@@ -1297,13 +1320,13 @@
         <v>10</v>
       </c>
       <c r="D52">
-        <v>589.7</v>
+        <v>589.70000000000005</v>
       </c>
       <c r="E52">
         <v>231428</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>6</v>
       </c>
@@ -1320,7 +1343,7 @@
         <v>125878</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>6</v>
       </c>
@@ -1337,7 +1360,7 @@
         <v>270396</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>6</v>
       </c>
@@ -1354,7 +1377,7 @@
         <v>184899</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>6</v>
       </c>
@@ -1371,7 +1394,7 @@
         <v>375570</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>6</v>
       </c>
@@ -1388,7 +1411,7 @@
         <v>399989</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>6</v>
       </c>
@@ -1399,13 +1422,13 @@
         <v>11</v>
       </c>
       <c r="D58">
-        <v>514.7</v>
+        <v>514.70000000000005</v>
       </c>
       <c r="E58">
         <v>455773</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>6</v>
       </c>
@@ -1416,13 +1439,13 @@
         <v>12</v>
       </c>
       <c r="D59">
-        <v>544.8</v>
+        <v>544.79999999999995</v>
       </c>
       <c r="E59">
         <v>462296</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>6</v>
       </c>
@@ -1439,7 +1462,7 @@
         <v>263307</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>6</v>
       </c>
@@ -1456,7 +1479,7 @@
         <v>220235</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>6</v>
       </c>
@@ -1473,7 +1496,7 @@
         <v>38047</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>6</v>
       </c>
@@ -1490,7 +1513,7 @@
         <v>308249</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>6</v>
       </c>
@@ -1507,7 +1530,7 @@
         <v>407261</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>6</v>
       </c>
@@ -1524,7 +1547,7 @@
         <v>305920</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>6</v>
       </c>
@@ -1541,7 +1564,7 @@
         <v>157848</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>6</v>
       </c>
@@ -1558,7 +1581,7 @@
         <v>112787</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>6</v>
       </c>
@@ -1575,7 +1598,7 @@
         <v>471269</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>6</v>
       </c>
@@ -1592,7 +1615,7 @@
         <v>41959</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>6</v>
       </c>
@@ -1609,7 +1632,7 @@
         <v>248576</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>6</v>
       </c>
@@ -1620,13 +1643,13 @@
         <v>14</v>
       </c>
       <c r="D71">
-        <v>647.2</v>
+        <v>647.20000000000005</v>
       </c>
       <c r="E71">
         <v>33545</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>6</v>
       </c>
@@ -1643,7 +1666,7 @@
         <v>375701</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>6</v>
       </c>
@@ -1660,7 +1683,7 @@
         <v>81087</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>6</v>
       </c>
@@ -1671,13 +1694,13 @@
         <v>12</v>
       </c>
       <c r="D74">
-        <v>594.3</v>
+        <v>594.29999999999995</v>
       </c>
       <c r="E74">
         <v>467600</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>6</v>
       </c>
@@ -1694,7 +1717,7 @@
         <v>333149</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>6</v>
       </c>
@@ -1711,7 +1734,7 @@
         <v>436880</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>6</v>
       </c>
@@ -1728,7 +1751,7 @@
         <v>87172</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>6</v>
       </c>
@@ -1745,7 +1768,7 @@
         <v>394325</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>6</v>
       </c>
@@ -1756,13 +1779,13 @@
         <v>12</v>
       </c>
       <c r="D79">
-        <v>623.2</v>
+        <v>623.20000000000005</v>
       </c>
       <c r="E79">
         <v>414070</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>6</v>
       </c>
@@ -1779,7 +1802,7 @@
         <v>277426</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>6</v>
       </c>
@@ -1796,7 +1819,7 @@
         <v>197789</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>6</v>
       </c>
@@ -1813,7 +1836,7 @@
         <v>255167</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>6</v>
       </c>
@@ -1830,7 +1853,7 @@
         <v>177381</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>6</v>
       </c>
@@ -1847,7 +1870,7 @@
         <v>118506</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>6</v>
       </c>
@@ -1864,7 +1887,7 @@
         <v>129751</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>6</v>
       </c>
@@ -1881,7 +1904,7 @@
         <v>481079</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>6</v>
       </c>
@@ -1898,7 +1921,7 @@
         <v>388452</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>6</v>
       </c>
@@ -1909,13 +1932,13 @@
         <v>11</v>
       </c>
       <c r="D88">
-        <v>570.3</v>
+        <v>570.29999999999995</v>
       </c>
       <c r="E88">
         <v>54698</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>6</v>
       </c>
@@ -1932,7 +1955,7 @@
         <v>130078</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>6</v>
       </c>
@@ -1949,7 +1972,7 @@
         <v>35708</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>6</v>
       </c>
@@ -1966,7 +1989,7 @@
         <v>374050</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>7</v>
       </c>
@@ -1977,13 +2000,13 @@
         <v>10</v>
       </c>
       <c r="D92">
-        <v>585.3</v>
+        <v>585.29999999999995</v>
       </c>
       <c r="E92">
         <v>485298</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>7</v>
       </c>
@@ -1994,13 +2017,13 @@
         <v>11</v>
       </c>
       <c r="D93">
-        <v>543.7</v>
+        <v>543.70000000000005</v>
       </c>
       <c r="E93">
         <v>406393</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>7</v>
       </c>
@@ -2017,7 +2040,7 @@
         <v>153983</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>7</v>
       </c>
@@ -2034,7 +2057,7 @@
         <v>480486</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>7</v>
       </c>
@@ -2045,13 +2068,13 @@
         <v>14</v>
       </c>
       <c r="D96">
-        <v>526.8</v>
+        <v>526.79999999999995</v>
       </c>
       <c r="E96">
         <v>91295</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>7</v>
       </c>
@@ -2068,7 +2091,7 @@
         <v>239686</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>7</v>
       </c>
@@ -2085,7 +2108,7 @@
         <v>67254</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>7</v>
       </c>
@@ -2102,7 +2125,7 @@
         <v>304062</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>7</v>
       </c>
@@ -2119,7 +2142,7 @@
         <v>328987</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>7</v>
       </c>
@@ -2130,13 +2153,13 @@
         <v>14</v>
       </c>
       <c r="D101">
-        <v>527.8</v>
+        <v>527.79999999999995</v>
       </c>
       <c r="E101">
         <v>140975</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>7</v>
       </c>
@@ -2153,7 +2176,7 @@
         <v>490587</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>7</v>
       </c>
@@ -2170,7 +2193,7 @@
         <v>393616</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>7</v>
       </c>
@@ -2187,7 +2210,7 @@
         <v>303076</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>7</v>
       </c>
@@ -2204,7 +2227,7 @@
         <v>137796</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>7</v>
       </c>
@@ -2221,7 +2244,7 @@
         <v>289544</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>7</v>
       </c>
@@ -2238,7 +2261,7 @@
         <v>400002</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>7</v>
       </c>
@@ -2249,13 +2272,13 @@
         <v>11</v>
       </c>
       <c r="D108">
-        <v>540.8</v>
+        <v>540.79999999999995</v>
       </c>
       <c r="E108">
         <v>24499</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>7</v>
       </c>
@@ -2272,7 +2295,7 @@
         <v>26295</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>7</v>
       </c>
@@ -2289,7 +2312,7 @@
         <v>442515</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>7</v>
       </c>
@@ -2306,7 +2329,7 @@
         <v>163946</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>7</v>
       </c>
@@ -2317,13 +2340,13 @@
         <v>10</v>
       </c>
       <c r="D112">
-        <v>542.7</v>
+        <v>542.70000000000005</v>
       </c>
       <c r="E112">
         <v>408207</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -2340,7 +2363,7 @@
         <v>153629</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -2357,7 +2380,7 @@
         <v>97505</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -2374,7 +2397,7 @@
         <v>22869</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -2391,7 +2414,7 @@
         <v>114179</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -2408,7 +2431,7 @@
         <v>110272</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -2425,7 +2448,7 @@
         <v>155059</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -2442,7 +2465,7 @@
         <v>78871</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -2453,13 +2476,13 @@
         <v>13</v>
       </c>
       <c r="D120">
-        <v>548.2</v>
+        <v>548.20000000000005</v>
       </c>
       <c r="E120">
         <v>106416</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -2476,7 +2499,7 @@
         <v>352415</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -2493,7 +2516,7 @@
         <v>191890</v>
       </c>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -2510,7 +2533,7 @@
         <v>458741</v>
       </c>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -2527,7 +2550,7 @@
         <v>493125</v>
       </c>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -2544,7 +2567,7 @@
         <v>67333</v>
       </c>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -2561,7 +2584,7 @@
         <v>170810</v>
       </c>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -2578,7 +2601,7 @@
         <v>312890</v>
       </c>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -2595,7 +2618,7 @@
         <v>453006</v>
       </c>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>7</v>
       </c>
@@ -2606,13 +2629,13 @@
         <v>12</v>
       </c>
       <c r="D129">
-        <v>572.7</v>
+        <v>572.70000000000005</v>
       </c>
       <c r="E129">
         <v>389599</v>
       </c>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>7</v>
       </c>
@@ -2629,7 +2652,7 @@
         <v>225615</v>
       </c>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>7</v>
       </c>
@@ -2640,13 +2663,13 @@
         <v>14</v>
       </c>
       <c r="D131">
-        <v>525.2</v>
+        <v>525.20000000000005</v>
       </c>
       <c r="E131">
         <v>65714</v>
       </c>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>7</v>
       </c>
@@ -2663,7 +2686,7 @@
         <v>125983</v>
       </c>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>7</v>
       </c>
@@ -2674,13 +2697,13 @@
         <v>11</v>
       </c>
       <c r="D133">
-        <v>519.8</v>
+        <v>519.79999999999995</v>
       </c>
       <c r="E133">
         <v>486960</v>
       </c>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>7</v>
       </c>
@@ -2697,7 +2720,7 @@
         <v>102989</v>
       </c>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>7</v>
       </c>
@@ -2714,7 +2737,7 @@
         <v>318356</v>
       </c>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>7</v>
       </c>
@@ -2731,7 +2754,7 @@
         <v>315972</v>
       </c>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>8</v>
       </c>
@@ -2742,13 +2765,13 @@
         <v>10</v>
       </c>
       <c r="D137">
-        <v>525.3</v>
+        <v>525.29999999999995</v>
       </c>
       <c r="E137">
         <v>431927</v>
       </c>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>8</v>
       </c>
@@ -2759,13 +2782,13 @@
         <v>11</v>
       </c>
       <c r="D138">
-        <v>530.3</v>
+        <v>530.29999999999995</v>
       </c>
       <c r="E138">
         <v>135294</v>
       </c>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>8</v>
       </c>
@@ -2782,7 +2805,7 @@
         <v>479451</v>
       </c>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>8</v>
       </c>
@@ -2799,7 +2822,7 @@
         <v>397812</v>
       </c>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>8</v>
       </c>
@@ -2816,7 +2839,7 @@
         <v>288246</v>
       </c>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>8</v>
       </c>
@@ -2833,7 +2856,7 @@
         <v>46641</v>
       </c>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>8</v>
       </c>
@@ -2850,7 +2873,7 @@
         <v>185656</v>
       </c>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>8</v>
       </c>
@@ -2861,13 +2884,13 @@
         <v>12</v>
       </c>
       <c r="D144">
-        <v>554.8</v>
+        <v>554.79999999999995</v>
       </c>
       <c r="E144">
         <v>385890</v>
       </c>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>8</v>
       </c>
@@ -2884,7 +2907,7 @@
         <v>465101</v>
       </c>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>8</v>
       </c>
@@ -2901,7 +2924,7 @@
         <v>293237</v>
       </c>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>8</v>
       </c>
@@ -2918,7 +2941,7 @@
         <v>38070</v>
       </c>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>8</v>
       </c>
@@ -2935,7 +2958,7 @@
         <v>250785</v>
       </c>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>8</v>
       </c>
@@ -2952,7 +2975,7 @@
         <v>196089</v>
       </c>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>8</v>
       </c>
@@ -2969,7 +2992,7 @@
         <v>413002</v>
       </c>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>8</v>
       </c>
@@ -2980,13 +3003,13 @@
         <v>14</v>
       </c>
       <c r="D151">
-        <v>553.3</v>
+        <v>553.29999999999995</v>
       </c>
       <c r="E151">
         <v>229141</v>
       </c>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>8</v>
       </c>
@@ -3003,7 +3026,7 @@
         <v>170262</v>
       </c>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>8</v>
       </c>
@@ -3020,7 +3043,7 @@
         <v>462905</v>
       </c>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>8</v>
       </c>
@@ -3031,13 +3054,13 @@
         <v>12</v>
       </c>
       <c r="D154">
-        <v>515.2</v>
+        <v>515.20000000000005</v>
       </c>
       <c r="E154">
         <v>159788</v>
       </c>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>8</v>
       </c>
@@ -3054,7 +3077,7 @@
         <v>239963</v>
       </c>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>8</v>
       </c>
@@ -3065,13 +3088,13 @@
         <v>14</v>
       </c>
       <c r="D156">
-        <v>525.8</v>
+        <v>525.79999999999995</v>
       </c>
       <c r="E156">
         <v>352460</v>
       </c>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>8</v>
       </c>
@@ -3088,7 +3111,7 @@
         <v>278067</v>
       </c>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>8</v>
       </c>
@@ -3105,7 +3128,7 @@
         <v>90031</v>
       </c>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>8</v>
       </c>
@@ -3122,7 +3145,7 @@
         <v>489645</v>
       </c>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>8</v>
       </c>
@@ -3139,7 +3162,7 @@
         <v>426619</v>
       </c>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>8</v>
       </c>
@@ -3156,7 +3179,7 @@
         <v>52097</v>
       </c>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>8</v>
       </c>
@@ -3173,7 +3196,7 @@
         <v>250229</v>
       </c>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>8</v>
       </c>
@@ -3190,7 +3213,7 @@
         <v>138834</v>
       </c>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>8</v>
       </c>
@@ -3201,13 +3224,13 @@
         <v>12</v>
       </c>
       <c r="D164">
-        <v>615.7</v>
+        <v>615.70000000000005</v>
       </c>
       <c r="E164">
         <v>201372</v>
       </c>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>8</v>
       </c>
@@ -3224,7 +3247,7 @@
         <v>304821</v>
       </c>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>8</v>
       </c>
@@ -3241,7 +3264,7 @@
         <v>90313</v>
       </c>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>8</v>
       </c>
@@ -3258,7 +3281,7 @@
         <v>409957</v>
       </c>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>8</v>
       </c>
@@ -3269,13 +3292,13 @@
         <v>11</v>
       </c>
       <c r="D168">
-        <v>517.7</v>
+        <v>517.70000000000005</v>
       </c>
       <c r="E168">
         <v>133632</v>
       </c>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>8</v>
       </c>
@@ -3292,7 +3315,7 @@
         <v>493351</v>
       </c>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>8</v>
       </c>
@@ -3309,7 +3332,7 @@
         <v>396836</v>
       </c>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>8</v>
       </c>
@@ -3326,7 +3349,7 @@
         <v>107235</v>
       </c>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>8</v>
       </c>
@@ -3343,7 +3366,7 @@
         <v>445309</v>
       </c>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>8</v>
       </c>
@@ -3360,7 +3383,7 @@
         <v>482894</v>
       </c>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>8</v>
       </c>
@@ -3377,7 +3400,7 @@
         <v>256175</v>
       </c>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>8</v>
       </c>
@@ -3394,7 +3417,7 @@
         <v>114476</v>
       </c>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>8</v>
       </c>
@@ -3411,7 +3434,7 @@
         <v>230706</v>
       </c>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>8</v>
       </c>
@@ -3428,7 +3451,7 @@
         <v>48251</v>
       </c>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>8</v>
       </c>
@@ -3445,7 +3468,7 @@
         <v>52217</v>
       </c>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>8</v>
       </c>
@@ -3462,7 +3485,7 @@
         <v>28308</v>
       </c>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -3479,7 +3502,7 @@
         <v>120235</v>
       </c>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A181" t="s">
         <v>8</v>
       </c>
@@ -3496,7 +3519,7 @@
         <v>94740</v>
       </c>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A182" t="s">
         <v>9</v>
       </c>
@@ -3513,7 +3536,7 @@
         <v>25237</v>
       </c>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A183" t="s">
         <v>9</v>
       </c>
@@ -3530,7 +3553,7 @@
         <v>40056</v>
       </c>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A184" t="s">
         <v>9</v>
       </c>
@@ -3547,7 +3570,7 @@
         <v>154415</v>
       </c>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A185" t="s">
         <v>9</v>
       </c>
@@ -3564,7 +3587,7 @@
         <v>426716</v>
       </c>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A186" t="s">
         <v>9</v>
       </c>
@@ -3581,7 +3604,7 @@
         <v>133429</v>
       </c>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A187" t="s">
         <v>9</v>
       </c>
@@ -3598,7 +3621,7 @@
         <v>272764</v>
       </c>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A188" t="s">
         <v>9</v>
       </c>
@@ -3615,7 +3638,7 @@
         <v>87215</v>
       </c>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A189" t="s">
         <v>9</v>
       </c>
@@ -3632,7 +3655,7 @@
         <v>351186</v>
       </c>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A190" t="s">
         <v>9</v>
       </c>
@@ -3649,7 +3672,7 @@
         <v>259833</v>
       </c>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A191" t="s">
         <v>9</v>
       </c>
@@ -3666,7 +3689,7 @@
         <v>272377</v>
       </c>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A192" t="s">
         <v>9</v>
       </c>
@@ -3683,7 +3706,7 @@
         <v>475968</v>
       </c>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A193" t="s">
         <v>9</v>
       </c>
@@ -3700,7 +3723,7 @@
         <v>338717</v>
       </c>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A194" t="s">
         <v>9</v>
       </c>
@@ -3717,7 +3740,7 @@
         <v>43049</v>
       </c>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A195" t="s">
         <v>9</v>
       </c>
@@ -3734,7 +3757,7 @@
         <v>230677</v>
       </c>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A196" t="s">
         <v>9</v>
       </c>
@@ -3751,7 +3774,7 @@
         <v>453374</v>
       </c>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A197" t="s">
         <v>9</v>
       </c>
@@ -3768,7 +3791,7 @@
         <v>216489</v>
       </c>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
         <v>9</v>
       </c>
@@ -3785,7 +3808,7 @@
         <v>211232</v>
       </c>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
         <v>9</v>
       </c>
@@ -3802,7 +3825,7 @@
         <v>324119</v>
       </c>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
         <v>9</v>
       </c>
@@ -3819,7 +3842,7 @@
         <v>71991</v>
       </c>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
         <v>9</v>
       </c>
@@ -3836,7 +3859,7 @@
         <v>208751</v>
       </c>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
         <v>9</v>
       </c>
@@ -3853,7 +3876,7 @@
         <v>373151</v>
       </c>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>9</v>
       </c>
@@ -3870,7 +3893,7 @@
         <v>239295</v>
       </c>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
         <v>9</v>
       </c>
@@ -3887,7 +3910,7 @@
         <v>485585</v>
       </c>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A205" t="s">
         <v>9</v>
       </c>
@@ -3904,7 +3927,7 @@
         <v>31938</v>
       </c>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A206" t="s">
         <v>9</v>
       </c>
@@ -3921,7 +3944,7 @@
         <v>383186</v>
       </c>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A207" t="s">
         <v>9</v>
       </c>
@@ -3938,7 +3961,7 @@
         <v>375754</v>
       </c>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>9</v>
       </c>
@@ -3955,7 +3978,7 @@
         <v>58304</v>
       </c>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A209" t="s">
         <v>9</v>
       </c>
@@ -3972,7 +3995,7 @@
         <v>351593</v>
       </c>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A210" t="s">
         <v>9</v>
       </c>
@@ -3989,7 +4012,7 @@
         <v>499243</v>
       </c>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A211" t="s">
         <v>9</v>
       </c>
@@ -4006,7 +4029,7 @@
         <v>320638</v>
       </c>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A212" t="s">
         <v>9</v>
       </c>
@@ -4023,7 +4046,7 @@
         <v>405777</v>
       </c>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A213" t="s">
         <v>9</v>
       </c>
@@ -4040,7 +4063,7 @@
         <v>120386</v>
       </c>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A214" t="s">
         <v>9</v>
       </c>
@@ -4057,7 +4080,7 @@
         <v>108668</v>
       </c>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A215" t="s">
         <v>9</v>
       </c>
@@ -4074,7 +4097,7 @@
         <v>134585</v>
       </c>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A216" t="s">
         <v>9</v>
       </c>
@@ -4091,7 +4114,7 @@
         <v>339602</v>
       </c>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A217" t="s">
         <v>9</v>
       </c>
@@ -4108,7 +4131,7 @@
         <v>302502</v>
       </c>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A218" t="s">
         <v>9</v>
       </c>
@@ -4125,7 +4148,7 @@
         <v>177164</v>
       </c>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>9</v>
       </c>
@@ -4142,7 +4165,7 @@
         <v>31338</v>
       </c>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>9</v>
       </c>
@@ -4159,7 +4182,7 @@
         <v>80692</v>
       </c>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A221" t="s">
         <v>9</v>
       </c>
@@ -4176,7 +4199,7 @@
         <v>240156</v>
       </c>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A222" t="s">
         <v>9</v>
       </c>
@@ -4193,7 +4216,7 @@
         <v>38888</v>
       </c>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>9</v>
       </c>
@@ -4210,7 +4233,7 @@
         <v>186807</v>
       </c>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>9</v>
       </c>
@@ -4227,7 +4250,7 @@
         <v>216582</v>
       </c>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>9</v>
       </c>
@@ -4244,7 +4267,7 @@
         <v>448127</v>
       </c>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>9</v>
       </c>
